--- a/StructureDefinition-shipment-specimen.xlsx
+++ b/StructureDefinition-shipment-specimen.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T02:24:20+00:00</t>
+    <t>2026-10-12T15:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-shipment-specimen.xlsx
+++ b/StructureDefinition-shipment-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T15:07:11+00:00</t>
+    <t>2026-10-12T15:22:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-shipment-specimen.xlsx
+++ b/StructureDefinition-shipment-specimen.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T15:22:52+00:00</t>
+    <t>2026-10-14T21:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
